--- a/Lab_stuff/Course_materials/BTC181-LabTechniques/Attachments/VG007 Attachment - Template and Example PCR Master Mix Reaction Sheet.xlsx
+++ b/Lab_stuff/Course_materials/BTC181-LabTechniques/Attachments/VG007 Attachment - Template and Example PCR Master Mix Reaction Sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\working\waccache\PA1PEPF00128CF6\EXCELCNV\6b3b9061-7fba-4cc7-91e3-20ea4f7b7984\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{9806A77A-0A9F-4E73-90B8-A11DCAD52AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C67AA2A-1443-40F5-B4AF-3B414B7ADCDC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5214051-3E31-4E94-A769-2BA085A8AAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-60" yWindow="-60" windowWidth="15480" windowHeight="11640" tabRatio="841" xr2:uid="{F8E01F73-555A-421F-9899-E5294F529936}"/>
   </bookViews>
@@ -38,7 +38,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
+  <si>
+    <t>PCR Reaction Experiment</t>
+  </si>
   <si>
     <t>Performed by and date: __________________________</t>
   </si>
@@ -128,6 +131,19 @@
   </si>
   <si>
     <t>for cDNA; use lower case f and r for genomic DNA. See example above.</t>
+  </si>
+  <si>
+    <t>After PCR reactions have finished, perform PCR cleanup steps as instructed in VG007 SOP</t>
+  </si>
+  <si>
+    <t>Performed | Witness (inital and date)</t>
+  </si>
+  <si>
+    <t>PCR cleanup has been performed on each reaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
   <si>
     <t xml:space="preserve">Run at least 1 ul of cleaned PCR product with 1 ul Lamda DNA in a separate lane for quantification and visualization in 1% gel </t>
@@ -278,7 +294,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -313,6 +329,11 @@
       <color rgb="FF242424"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -328,7 +349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -472,11 +493,191 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -513,11 +714,51 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,6 +774,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -825,7 +1083,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="21.42578125" customWidth="1"/>
@@ -838,232 +1096,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
       <c r="C1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="21" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="18" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="26" t="s">
+      <c r="E3" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="F3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="G3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="H3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="I3" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="J3" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="K3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="26" t="s">
+      <c r="L3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="M3" s="25" t="s">
         <v>13</v>
       </c>
+      <c r="N3" s="25" t="s">
+        <v>14</v>
+      </c>
       <c r="O3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="E4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="26" t="s">
-        <v>16</v>
+      <c r="E4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="26" t="s">
-        <v>16</v>
+      <c r="E5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="O5" s="4">
         <f>SUM(E5:N5)</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N6" s="26" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N6" s="25" t="s">
+        <v>17</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" ht="30.75">
       <c r="A7" s="20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="26" t="s">
-        <v>16</v>
+        <v>24</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N7" s="25" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="C9" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1080,8 +1341,8 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="23"/>
     </row>
     <row r="11" spans="1:16">
       <c r="C11">
@@ -1098,7 +1359,7 @@
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="23"/>
+      <c r="O11" s="22"/>
     </row>
     <row r="12" spans="1:16">
       <c r="C12">
@@ -1455,9 +1716,9 @@
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-    </row>
-    <row r="33" spans="3:14">
+      <c r="O32" s="26"/>
+    </row>
+    <row r="33" spans="3:16">
       <c r="C33">
         <v>24</v>
       </c>
@@ -1471,14 +1732,15 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="35" spans="3:14" ht="13.5" thickBot="1">
+      <c r="N33" s="24"/>
+      <c r="O33" s="23"/>
+    </row>
+    <row r="35" spans="3:16" ht="13.5" thickBot="1">
       <c r="C35" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="3:14">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="3:16">
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
@@ -1491,19 +1753,19 @@
       <c r="L36" s="10"/>
       <c r="M36" s="11"/>
     </row>
-    <row r="37" spans="3:14">
+    <row r="37" spans="3:16">
       <c r="C37" s="12"/>
       <c r="M37" s="13"/>
     </row>
-    <row r="38" spans="3:14">
+    <row r="38" spans="3:16">
       <c r="C38" s="12"/>
       <c r="M38" s="13"/>
     </row>
-    <row r="39" spans="3:14">
+    <row r="39" spans="3:16">
       <c r="C39" s="12"/>
       <c r="M39" s="13"/>
     </row>
-    <row r="40" spans="3:14" ht="13.5" thickBot="1">
+    <row r="40" spans="3:16" ht="13.5" thickBot="1">
       <c r="C40" s="14"/>
       <c r="D40" s="15"/>
       <c r="E40" s="15"/>
@@ -1516,93 +1778,127 @@
       <c r="L40" s="15"/>
       <c r="M40" s="16"/>
     </row>
-    <row r="41" spans="3:14">
+    <row r="41" spans="3:16">
       <c r="C41" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="3:14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="3:16">
       <c r="D42" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="45" spans="3:14">
-      <c r="C45" s="19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="46" spans="3:14" ht="13.5" thickBot="1">
-      <c r="D46" t="s">
+    <row r="44" spans="3:16" ht="29.25" customHeight="1">
+      <c r="C44" s="27" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="47" spans="3:14">
-      <c r="C47" s="22" t="s">
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="11"/>
-    </row>
-    <row r="48" spans="3:14">
-      <c r="C48" s="12"/>
-      <c r="H48" s="13"/>
+      <c r="P44" s="43"/>
+    </row>
+    <row r="45" spans="3:16" ht="24">
+      <c r="C45" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D45" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="3:16">
+      <c r="C47" s="19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="3:16">
+      <c r="C48" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="49" spans="3:8">
-      <c r="C49" s="12"/>
-      <c r="H49" s="13"/>
+      <c r="C49" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="35"/>
     </row>
     <row r="50" spans="3:8">
-      <c r="C50" s="12"/>
-      <c r="H50" s="13"/>
+      <c r="C50" s="36"/>
+      <c r="H50" s="37"/>
     </row>
     <row r="51" spans="3:8">
-      <c r="C51" s="12"/>
-      <c r="H51" s="13"/>
+      <c r="C51" s="36"/>
+      <c r="H51" s="37"/>
     </row>
     <row r="52" spans="3:8">
-      <c r="C52" s="12"/>
-      <c r="H52" s="13"/>
+      <c r="C52" s="36"/>
+      <c r="H52" s="37"/>
     </row>
     <row r="53" spans="3:8">
-      <c r="C53" s="12"/>
-      <c r="H53" s="13"/>
+      <c r="C53" s="36"/>
+      <c r="H53" s="37"/>
     </row>
     <row r="54" spans="3:8">
-      <c r="C54" s="12"/>
-      <c r="H54" s="13"/>
+      <c r="C54" s="36"/>
+      <c r="H54" s="37"/>
     </row>
     <row r="55" spans="3:8">
-      <c r="C55" s="12"/>
-      <c r="H55" s="13"/>
+      <c r="C55" s="36"/>
+      <c r="H55" s="37"/>
     </row>
     <row r="56" spans="3:8">
-      <c r="C56" s="12"/>
-      <c r="H56" s="13"/>
+      <c r="C56" s="36"/>
+      <c r="H56" s="37"/>
     </row>
     <row r="57" spans="3:8">
-      <c r="C57" s="12"/>
-      <c r="H57" s="13"/>
+      <c r="C57" s="36"/>
+      <c r="H57" s="37"/>
     </row>
     <row r="58" spans="3:8">
-      <c r="C58" s="12"/>
-      <c r="H58" s="13"/>
+      <c r="C58" s="36"/>
+      <c r="H58" s="37"/>
     </row>
     <row r="59" spans="3:8">
-      <c r="C59" s="12"/>
-      <c r="H59" s="13"/>
-    </row>
-    <row r="60" spans="3:8" ht="13.5" thickBot="1">
-      <c r="C60" s="14"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
-      <c r="H60" s="16"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="40"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="D45:N45"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="65" orientation="landscape" r:id="rId1"/>
 </worksheet>
@@ -1633,14 +1929,14 @@
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G1"/>
       <c r="N1" s="8"/>
@@ -1650,58 +1946,58 @@
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="2" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="B4" s="3"/>
       <c r="N4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -1718,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="17.100000000000001" customHeight="1">
       <c r="A6" s="3"/>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -2149,7 +2445,7 @@
     </row>
     <row r="32" spans="1:13" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="17.100000000000001" customHeight="1">
@@ -2192,27 +2488,27 @@
     </row>
     <row r="38" spans="1:11" ht="17.100000000000001" customHeight="1">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="17.100000000000001" customHeight="1">
       <c r="B39" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="17.100000000000001" customHeight="1">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="B41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="17.100000000000001" customHeight="1">
       <c r="A42" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
@@ -2300,46 +2596,46 @@
   <sheetData>
     <row r="3" spans="1:14">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -2347,41 +2643,41 @@
       <c r="B4" s="3"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4">
         <f>13.9-4</f>
@@ -2419,13 +2715,13 @@
         <v>19.899999999999999</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <f>12*C5</f>
@@ -2477,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -2496,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -2515,7 +2811,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -2534,7 +2830,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -2553,7 +2849,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -2572,7 +2868,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -2591,7 +2887,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -2610,7 +2906,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2629,7 +2925,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -2645,7 +2941,7 @@
     </row>
     <row r="17" spans="1:11" ht="13.5" thickBot="1">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2688,27 +2984,27 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="B24" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="13.5" thickBot="1">
       <c r="B26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="9" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
